--- a/gpt_agents-master/Linear Regression/Fundamentalist Trader Positive.xlsx
+++ b/gpt_agents-master/Linear Regression/Fundamentalist Trader Positive.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sidney\Documents\Year 3\Final Year Project\gpt_agents-master\Linear Regression\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sidney\Documents\Year_3\Final Year Project\gpt_agents-master\Linear Regression\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ADA9E713-3491-4748-8401-2C9FF16FA401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9879CEA9-4642-42AE-ACC7-99D4B6DDEDB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19260" yWindow="2830" windowWidth="18140" windowHeight="15370" xr2:uid="{8FE0B354-240A-4713-9796-0CC0D16DF899}"/>
+    <workbookView xWindow="39370" yWindow="3260" windowWidth="18140" windowHeight="15370" xr2:uid="{8FE0B354-240A-4713-9796-0CC0D16DF899}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,16 +38,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t>predicted_price</t>
-  </si>
-  <si>
-    <t>actual_price</t>
-  </si>
-  <si>
     <t>time_step</t>
   </si>
   <si>
     <t>agent_id</t>
+  </si>
+  <si>
+    <t>mean_predicted_price</t>
+  </si>
+  <si>
+    <t>mean_actual_price</t>
   </si>
 </sst>
 </file>
@@ -428,16 +428,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
